--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-common.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-common.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport</t>
+    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -375,7 +375,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -591,7 +591,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -815,7 +815,7 @@
     <t>診断レポートを説明するコードまたは名前</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Group|Device|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Group|4.0.1|Device|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -869,7 +869,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -962,7 +962,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1006,7 +1006,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1029,7 +1029,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1132,7 +1132,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1176,7 +1176,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1515,7 +1515,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="178.02734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="212.125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1530,7 +1530,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-common.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-diagnosticreport-common.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -375,7 +375,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ImmunizationRecommendation|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -591,7 +591,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -815,7 +815,7 @@
     <t>診断レポートを説明するコードまたは名前</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Group|4.0.1|Device|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Group|Device|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -869,7 +869,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -962,7 +962,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam)
 </t>
   </si>
   <si>
@@ -1006,7 +1006,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1029,7 +1029,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1)
+    <t xml:space="preserve">Reference(Observation)
 </t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(ImagingStudy)
 </t>
   </si>
   <si>
@@ -1132,7 +1132,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media|4.0.1)
+    <t xml:space="preserve">Reference(Media)
 </t>
   </si>
   <si>
@@ -1176,7 +1176,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1515,7 +1515,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="212.125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="178.02734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1530,7 +1530,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
